--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83573284-43C5-46BB-ACEA-8FA5DA818900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE80110-6CAF-4ABE-A65B-95F331FA4A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -1742,26 +1742,26 @@
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="5" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="6.33203125" hidden="1" customWidth="1"/>
-    <col min="18" max="19" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="21" max="22" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="23" max="29" width="4.6640625" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="5.44140625" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7.33203125" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="6.33203125" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" customWidth="1"/>
+    <col min="9" max="10" width="8.33203125" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="12" max="13" width="8.33203125" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" customWidth="1"/>
+    <col min="15" max="16" width="8.33203125" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" customWidth="1"/>
+    <col min="18" max="19" width="8.33203125" customWidth="1"/>
+    <col min="20" max="20" width="7.33203125" customWidth="1"/>
+    <col min="21" max="22" width="8.33203125" customWidth="1"/>
+    <col min="23" max="29" width="4.6640625" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.33203125" customWidth="1"/>
+    <col min="32" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="33" width="8.109375" customWidth="1"/>
     <col min="34" max="34" width="33.6640625" customWidth="1"/>
     <col min="35" max="35" width="63.77734375" customWidth="1"/>
     <col min="36" max="36" width="4.44140625" customWidth="1"/>
@@ -5689,8 +5689,8 @@
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" customWidth="1"/>
     <col min="9" max="10" width="8.33203125" customWidth="1"/>
@@ -5707,8 +5707,8 @@
     <col min="31" max="31" width="7.33203125" customWidth="1"/>
     <col min="32" max="32" width="6.33203125" customWidth="1"/>
     <col min="33" max="33" width="8.109375" customWidth="1"/>
-    <col min="34" max="34" width="33.6640625" customWidth="1"/>
-    <col min="35" max="35" width="78.21875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33.6640625" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="78.21875" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="37" max="37" width="33.33203125" customWidth="1"/>
     <col min="38" max="38" width="8.33203125" customWidth="1"/>
@@ -8124,8 +8124,10 @@
   <dimension ref="A1:BA19"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="34" max="34" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="23.33203125" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="21.109375" hidden="1" customWidth="1"/>
     <col min="36" max="36" width="4.44140625" customWidth="1"/>
     <col min="37" max="37" width="33.33203125" customWidth="1"/>
     <col min="38" max="38" width="8.33203125" customWidth="1"/>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE80110-6CAF-4ABE-A65B-95F331FA4A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFBD78D-360D-483D-9C1B-C3C1E5701D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="356">
   <si>
     <t>2026-2027 賽季 新北國王 (TPBL) 例行賽球員攻守數據表 - 平均數據</t>
   </si>
@@ -1000,43 +1000,97 @@
     <t>國王在上半場落後局面下，第三節靠著林書緯外線串聯與沃許本禁區高低位配合打出 25:14 逆轉攻勢；雙洋將（肯刀爾、克雷格）本場進攻雖受限，但本土雙衛與內線護框展現衛冕軍韌性。</t>
   </si>
   <si>
-    <t>外線投射與擋拆拋投(三分佔比67%)</t>
-  </si>
-  <si>
-    <t>次戰打出真核表現，三分6投4中狂飆18分6助攻4籃板，正負值+20全場第一。</t>
-  </si>
-  <si>
-    <t>禁區終結與中距離跳投(兩分佔比100%)</t>
-  </si>
-  <si>
-    <t>內線穩健輸出17分9籃板並送出關鍵3火鍋，下半場攻守主宰力助隊逆轉。</t>
-  </si>
-  <si>
-    <t>突分切入與抄截快攻(兩分佔比73%)</t>
-  </si>
-  <si>
-    <t>先發出戰28分鐘貢獻14分4板3抄截，關鍵追分期防守施壓與推進效果顯著。</t>
-  </si>
-  <si>
-    <t>禁區衝搶與造犯規(罰球產量高)</t>
-  </si>
-  <si>
-    <t>雖手感欠佳但狂抓全場最高12籃板，靠防守拼搶與5罰全中在拉鋸期穩定局勢。</t>
-  </si>
-  <si>
-    <t>底角三分與轉換快攻(外線把握度高)</t>
-  </si>
-  <si>
-    <t>替補出戰17分鐘命中關鍵三分得5分，正負值+11為板凳最高，外線冷箭奇兵。</t>
-  </si>
-  <si>
-    <t>切入拋投與變速突破(衝擊禁區為主)</t>
-  </si>
-  <si>
-    <t>替補18分鐘貢獻10分3籃板3助攻，正負值+6，二陣持球切入造殺傷極具威脅。</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>【單場焦點對位交鋒】</t>
+  </si>
+  <si>
+    <t>禁區衝搶與造犯規為主(罰球產量極高)</t>
+  </si>
+  <si>
+    <t>場均20分12.5籃板2抄截，具備頂級衝擊力與籃板嗅覺，國王前場反擊發動機。</t>
+  </si>
+  <si>
+    <t>突破切入與轉換快攻(兩分佔比67%)</t>
+  </si>
+  <si>
+    <t>場均19分5籃板3助攻2抄截，攻防轉換推進箭頭，切入造殺傷極具破壞力。</t>
+  </si>
+  <si>
+    <t>突分切入與底角空檔(真實命中率63.2%)</t>
+  </si>
+  <si>
+    <t>場均15.5分5籃板1.5抄截，攻守兩端極為穩健，球隊外圍第一線大鎖與副攻手。</t>
+  </si>
+  <si>
+    <t>底角三分與外線砲火(三分命中率50%)</t>
+  </si>
+  <si>
+    <t>場均8分，三分命中率高達50%，具備冷箭屬性的高效率外線終結射手。</t>
+  </si>
+  <si>
+    <t>禁區高低位單打與中距離跳投(兩分100%)</t>
+  </si>
+  <si>
+    <t>場均13分9.5籃板1.5阻攻，禁區護框支柱與高位中樞，次戰下半場逆轉關鍵。</t>
+  </si>
+  <si>
+    <t>空間型前鋒與空手切入(eFG% 57.1%)</t>
+  </si>
+  <si>
+    <t>場均5分3.5籃板1阻攻1抄截，防守輪轉積極且跑動意識佳，優質鋒線輪替。</t>
+  </si>
+  <si>
+    <t>外線投射與擋拆發動(三分佔比53%)</t>
+  </si>
+  <si>
+    <t>場均12分5.5助攻5籃板，次戰三分6中4狂飆18分，球隊半場進攻組織大腦。</t>
+  </si>
+  <si>
+    <t>變速切入與拋投終結(助攻失誤比4.0)</t>
+  </si>
+  <si>
+    <t>場均7.5分2助攻2抄截，二陣持球突擊速度極快，兼具出色的失誤控制能力。</t>
+  </si>
+  <si>
+    <t>側翼防守與外線牽制(持球比重降低)</t>
+  </si>
+  <si>
+    <t>開季出賽2場主打團隊防守與策應，持續調整外圍進攻節奏與出手信心。</t>
+  </si>
+  <si>
+    <t>外線定點射手(待賽程展開)</t>
+  </si>
+  <si>
+    <t>開季出賽1場，具備穩健的三分投射經驗，替補席外圍空間拉開點。</t>
+  </si>
+  <si>
+    <t>替補後衛與防守拼搶(積極度高)</t>
+  </si>
+  <si>
+    <t>替補出賽2場貢獻1.5籃板與抄截，防守端積極度高，提供後場短暫輪休調節。</t>
+  </si>
+  <si>
+    <t>禁區肉搏型中鋒(低位掩護)</t>
+  </si>
+  <si>
+    <t>出賽2場提供扎實單防卡位與高位掩護，分擔主力內線犯規負擔。</t>
+  </si>
+  <si>
+    <t>鋒線切入與轉換快攻(衝搶積極)</t>
+  </si>
+  <si>
+    <t>出賽1場靠罰球進帳2分1籃板，機動性鋒線替補，防守端拼搶意識強。</t>
+  </si>
+  <si>
+    <t>外線投射射手(待賽程展開)</t>
+  </si>
+  <si>
+    <t>開季出賽1場，具備外線跳投能力，持續爭取主要輪替上場時間。</t>
+  </si>
+  <si>
+    <t>禁區傳統大洋將(待例行賽出賽)</t>
+  </si>
+  <si>
+    <t>待例行賽賽程展開 / 先列入註冊名單與數據架構。</t>
   </si>
 </sst>
 </file>
@@ -2214,10 +2268,10 @@
         <v>1</v>
       </c>
       <c r="AH5" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AI5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AJ5" s="17"/>
       <c r="AK5" t="s">
@@ -2383,11 +2437,11 @@
       <c r="AG6" s="14">
         <v>0.75</v>
       </c>
-      <c r="AH6" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI6" s="13" t="s">
-        <v>337</v>
+      <c r="AH6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>329</v>
       </c>
       <c r="AJ6" s="17"/>
       <c r="AK6" t="s">
@@ -2554,10 +2608,10 @@
         <v>0.6</v>
       </c>
       <c r="AH7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AI7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AJ7" s="17"/>
       <c r="AK7" t="s">
@@ -2724,10 +2778,10 @@
         <v>2</v>
       </c>
       <c r="AH8" t="s">
+        <v>332</v>
+      </c>
+      <c r="AI8" t="s">
         <v>333</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>334</v>
       </c>
       <c r="AJ8" s="17"/>
       <c r="AK8" t="s">
@@ -2868,10 +2922,10 @@
         <v>0.83</v>
       </c>
       <c r="AH9" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AI9" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AJ9" s="17"/>
       <c r="AK9" t="s">
@@ -3011,10 +3065,10 @@
       <c r="AG10" s="14">
         <v>0</v>
       </c>
-      <c r="AH10" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI10" s="13" t="s">
+      <c r="AH10" t="s">
+        <v>336</v>
+      </c>
+      <c r="AI10" t="s">
         <v>337</v>
       </c>
       <c r="AJ10" s="17"/>
@@ -3156,10 +3210,10 @@
         <v>2.75</v>
       </c>
       <c r="AH11" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="AI11" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="AJ11" s="17"/>
       <c r="AK11" t="s">
@@ -3300,10 +3354,10 @@
         <v>4</v>
       </c>
       <c r="AH12" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AI12" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AJ12" s="17"/>
       <c r="AK12" t="s">
@@ -3443,11 +3497,11 @@
       <c r="AG13" s="14">
         <v>0.33</v>
       </c>
-      <c r="AH13" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="AI13" s="13" t="s">
-        <v>158</v>
+      <c r="AH13" t="s">
+        <v>342</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>343</v>
       </c>
       <c r="AJ13" s="17"/>
       <c r="AK13" t="s">
@@ -3587,11 +3641,11 @@
       <c r="AG14" s="14">
         <v>0</v>
       </c>
-      <c r="AH14" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI14" s="13" t="s">
-        <v>337</v>
+      <c r="AH14" t="s">
+        <v>344</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>345</v>
       </c>
       <c r="AJ14" s="17"/>
       <c r="AK14" s="21"/>
@@ -3717,11 +3771,11 @@
       <c r="AG15" s="14">
         <v>1</v>
       </c>
-      <c r="AH15" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI15" s="13" t="s">
-        <v>166</v>
+      <c r="AH15" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>347</v>
       </c>
       <c r="AJ15" s="17"/>
       <c r="AK15" s="21"/>
@@ -3847,11 +3901,11 @@
       <c r="AG16" s="14">
         <v>0</v>
       </c>
-      <c r="AH16" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI16" s="13" t="s">
-        <v>337</v>
+      <c r="AH16" t="s">
+        <v>348</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>349</v>
       </c>
       <c r="AJ16" s="17"/>
       <c r="AK16" s="21"/>
@@ -3977,11 +4031,11 @@
       <c r="AG17" s="14">
         <v>0</v>
       </c>
-      <c r="AH17" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI17" s="13" t="s">
-        <v>337</v>
+      <c r="AH17" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>351</v>
       </c>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="21"/>
@@ -4107,11 +4161,11 @@
       <c r="AG18" s="14">
         <v>0</v>
       </c>
-      <c r="AH18" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI18" s="13" t="s">
-        <v>337</v>
+      <c r="AH18" t="s">
+        <v>352</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>353</v>
       </c>
       <c r="AJ18" s="17"/>
       <c r="AK18" s="21"/>
@@ -4237,11 +4291,11 @@
       <c r="AG19" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="AH19" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="AI19" s="13" t="s">
-        <v>337</v>
+      <c r="AH19" t="s">
+        <v>354</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>355</v>
       </c>
       <c r="AJ19" s="21"/>
       <c r="AK19" s="21"/>
@@ -8220,7 +8274,7 @@
       <c r="AX3" s="9"/>
       <c r="AY3" s="8"/>
       <c r="AZ3" s="9" t="s">
-        <v>219</v>
+        <v>325</v>
       </c>
       <c r="BA3" s="9"/>
     </row>

--- a/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
+++ b/data/season2026/2026-2027 TPBL 例行賽球員數據表 - 新北國王.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFBD78D-360D-483D-9C1B-C3C1E5701D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF2F285-2065-4EC8-98D2-11F831B55301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="平均數據" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="355">
   <si>
     <t>2026-2027 賽季 新北國王 (TPBL) 例行賽球員攻守數據表 - 平均數據</t>
   </si>
@@ -680,9 +680,6 @@
   </si>
   <si>
     <t>【單場最佳陣容與搭檔效益】</t>
-  </si>
-  <si>
-    <t>【單場焦點對位交鋒 (WOWY: 克雷格 vs 夢想家林俊吉)】</t>
   </si>
   <si>
     <t>在場時間</t>
@@ -2268,17 +2265,17 @@
         <v>1</v>
       </c>
       <c r="AH5" t="s">
+        <v>325</v>
+      </c>
+      <c r="AI5" t="s">
         <v>326</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>327</v>
       </c>
       <c r="AJ5" s="17"/>
       <c r="AK5" t="s">
         <v>120</v>
       </c>
       <c r="AL5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AM5">
         <v>108.5</v>
@@ -2316,10 +2313,10 @@
       </c>
       <c r="AY5" s="17"/>
       <c r="AZ5" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BA5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -2334,7 +2331,7 @@
         <v>26.7</v>
       </c>
       <c r="BF5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2438,17 +2435,17 @@
         <v>0.75</v>
       </c>
       <c r="AH6" t="s">
+        <v>327</v>
+      </c>
+      <c r="AI6" t="s">
         <v>328</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>329</v>
       </c>
       <c r="AJ6" s="17"/>
       <c r="AK6" t="s">
         <v>111</v>
       </c>
       <c r="AL6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AM6">
         <v>108.8</v>
@@ -2467,7 +2464,7 @@
       </c>
       <c r="AR6" s="17"/>
       <c r="AS6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AT6" s="39">
         <v>0.55555555555555558</v>
@@ -2486,10 +2483,10 @@
       </c>
       <c r="AY6" s="17"/>
       <c r="AZ6" s="23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BA6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2504,7 +2501,7 @@
         <v>20.3</v>
       </c>
       <c r="BF6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2608,17 +2605,17 @@
         <v>0.6</v>
       </c>
       <c r="AH7" t="s">
+        <v>329</v>
+      </c>
+      <c r="AI7" t="s">
         <v>330</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>331</v>
       </c>
       <c r="AJ7" s="17"/>
       <c r="AK7" t="s">
         <v>69</v>
       </c>
       <c r="AL7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AM7">
         <v>112.4</v>
@@ -2656,10 +2653,10 @@
       </c>
       <c r="AY7" s="17"/>
       <c r="AZ7" s="23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="BA7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="BB7">
         <v>7</v>
@@ -2674,7 +2671,7 @@
         <v>6.8</v>
       </c>
       <c r="BF7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:58" ht="13.2" x14ac:dyDescent="0.25">
@@ -2778,17 +2775,17 @@
         <v>2</v>
       </c>
       <c r="AH8" t="s">
+        <v>331</v>
+      </c>
+      <c r="AI8" t="s">
         <v>332</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>333</v>
       </c>
       <c r="AJ8" s="17"/>
       <c r="AK8" t="s">
         <v>97</v>
       </c>
       <c r="AL8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AM8">
         <v>102.5</v>
@@ -2922,17 +2919,17 @@
         <v>0.83</v>
       </c>
       <c r="AH9" t="s">
+        <v>333</v>
+      </c>
+      <c r="AI9" t="s">
         <v>334</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>335</v>
       </c>
       <c r="AJ9" s="17"/>
       <c r="AK9" t="s">
         <v>151</v>
       </c>
       <c r="AL9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AM9">
         <v>101.2</v>
@@ -3066,17 +3063,17 @@
         <v>0</v>
       </c>
       <c r="AH10" t="s">
+        <v>335</v>
+      </c>
+      <c r="AI10" t="s">
         <v>336</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>337</v>
       </c>
       <c r="AJ10" s="17"/>
       <c r="AK10" t="s">
         <v>159</v>
       </c>
       <c r="AL10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AM10">
         <v>98.5</v>
@@ -3210,17 +3207,17 @@
         <v>2.75</v>
       </c>
       <c r="AH11" t="s">
+        <v>337</v>
+      </c>
+      <c r="AI11" t="s">
         <v>338</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>339</v>
       </c>
       <c r="AJ11" s="17"/>
       <c r="AK11" t="s">
         <v>83</v>
       </c>
       <c r="AL11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AM11">
         <v>101.5</v>
@@ -3354,17 +3351,17 @@
         <v>4</v>
       </c>
       <c r="AH12" t="s">
+        <v>339</v>
+      </c>
+      <c r="AI12" t="s">
         <v>340</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>341</v>
       </c>
       <c r="AJ12" s="17"/>
       <c r="AK12" t="s">
         <v>140</v>
       </c>
       <c r="AL12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AM12">
         <v>98.2</v>
@@ -3498,17 +3495,17 @@
         <v>0.33</v>
       </c>
       <c r="AH13" t="s">
+        <v>341</v>
+      </c>
+      <c r="AI13" t="s">
         <v>342</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>343</v>
       </c>
       <c r="AJ13" s="17"/>
       <c r="AK13" t="s">
         <v>130</v>
       </c>
       <c r="AL13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AM13">
         <v>88.5</v>
@@ -3642,10 +3639,10 @@
         <v>0</v>
       </c>
       <c r="AH14" t="s">
+        <v>343</v>
+      </c>
+      <c r="AI14" t="s">
         <v>344</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>345</v>
       </c>
       <c r="AJ14" s="17"/>
       <c r="AK14" s="21"/>
@@ -3772,10 +3769,10 @@
         <v>1</v>
       </c>
       <c r="AH15" t="s">
+        <v>345</v>
+      </c>
+      <c r="AI15" t="s">
         <v>346</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>347</v>
       </c>
       <c r="AJ15" s="17"/>
       <c r="AK15" s="21"/>
@@ -3902,10 +3899,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
+        <v>347</v>
+      </c>
+      <c r="AI16" t="s">
         <v>348</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>349</v>
       </c>
       <c r="AJ16" s="17"/>
       <c r="AK16" s="21"/>
@@ -4032,10 +4029,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
+        <v>349</v>
+      </c>
+      <c r="AI17" t="s">
         <v>350</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>351</v>
       </c>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="21"/>
@@ -4162,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="AH18" t="s">
+        <v>351</v>
+      </c>
+      <c r="AI18" t="s">
         <v>352</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>353</v>
       </c>
       <c r="AJ18" s="17"/>
       <c r="AK18" s="21"/>
@@ -4292,10 +4289,10 @@
         <v>180</v>
       </c>
       <c r="AH19" t="s">
+        <v>353</v>
+      </c>
+      <c r="AI19" t="s">
         <v>354</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>355</v>
       </c>
       <c r="AJ19" s="21"/>
       <c r="AK19" s="21"/>
@@ -5919,7 +5916,7 @@
       <c r="AX3" s="9"/>
       <c r="AY3" s="8"/>
       <c r="AZ3" s="9" t="s">
-        <v>219</v>
+        <v>324</v>
       </c>
       <c r="BA3" s="9"/>
     </row>
@@ -6034,32 +6031,32 @@
         <v>6</v>
       </c>
       <c r="AL4" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="AM4" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="AM4" s="11" t="s">
+      <c r="AN4" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="AN4" s="11" t="s">
+      <c r="AO4" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="AO4" s="11" t="s">
+      <c r="AP4" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="AP4" s="11" t="s">
+      <c r="AQ4" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="AQ4" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="AR4" s="10"/>
       <c r="AS4" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AT4" s="11" t="s">
         <v>186</v>
       </c>
       <c r="AU4" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AV4" s="11" t="s">
         <v>49</v>
@@ -6072,10 +6069,10 @@
       </c>
       <c r="AY4" s="10"/>
       <c r="AZ4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="BA4" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="BA4" s="11" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:53" ht="26.4" x14ac:dyDescent="0.25">
@@ -6227,10 +6224,10 @@
       </c>
       <c r="AY5" s="17"/>
       <c r="AZ5" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="BA5" s="23" t="s">
         <v>230</v>
-      </c>
-      <c r="BA5" s="23" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:53" ht="26.4" x14ac:dyDescent="0.25">
@@ -6382,10 +6379,10 @@
       </c>
       <c r="AY6" s="17"/>
       <c r="AZ6" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="BA6" s="23" t="s">
         <v>232</v>
-      </c>
-      <c r="BA6" s="23" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:53" ht="39.6" x14ac:dyDescent="0.25">
@@ -6537,10 +6534,10 @@
       </c>
       <c r="AY7" s="17"/>
       <c r="AZ7" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="BA7" s="23" t="s">
         <v>234</v>
-      </c>
-      <c r="BA7" s="23" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:53" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6673,7 +6670,7 @@
       </c>
       <c r="AR8" s="17"/>
       <c r="AS8" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AT8" s="11"/>
       <c r="AU8" s="25"/>
@@ -6814,7 +6811,7 @@
       </c>
       <c r="AR9" s="17"/>
       <c r="AS9" s="21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AT9" s="19">
         <v>1.104166666666667</v>
@@ -6965,7 +6962,7 @@
       </c>
       <c r="AR10" s="17"/>
       <c r="AS10" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AT10" s="22">
         <v>0.92708333333333337</v>
@@ -7116,7 +7113,7 @@
       </c>
       <c r="AR11" s="17"/>
       <c r="AS11" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AT11" s="22">
         <v>0.69444444444444442</v>
@@ -8204,7 +8201,7 @@
   <sheetData>
     <row r="1" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AH1" s="4"/>
       <c r="AI1" s="4"/>
@@ -8229,7 +8226,7 @@
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
@@ -8274,7 +8271,7 @@
       <c r="AX3" s="9"/>
       <c r="AY3" s="8"/>
       <c r="AZ3" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="BA3" s="9"/>
     </row>
@@ -8389,32 +8386,32 @@
         <v>6</v>
       </c>
       <c r="AL4" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="AM4" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="AM4" s="11" t="s">
+      <c r="AN4" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="AN4" s="11" t="s">
+      <c r="AO4" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="AO4" s="11" t="s">
+      <c r="AP4" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="AP4" s="11" t="s">
+      <c r="AQ4" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="AQ4" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="AR4" s="10"/>
       <c r="AS4" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AT4" s="11" t="s">
         <v>186</v>
       </c>
       <c r="AU4" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AV4" s="11" t="s">
         <v>49</v>
@@ -8427,15 +8424,15 @@
       </c>
       <c r="AY4" s="10"/>
       <c r="AZ4" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="BA4" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="BA4" s="11" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s">
         <v>131</v>
@@ -8453,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H5">
         <v>18</v>
@@ -8465,7 +8462,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -8474,7 +8471,7 @@
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O5">
         <v>4</v>
@@ -8483,7 +8480,7 @@
         <v>6</v>
       </c>
       <c r="Q5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R5">
         <v>2</v>
@@ -8525,13 +8522,13 @@
         <v>20</v>
       </c>
       <c r="AE5" t="s">
+        <v>244</v>
+      </c>
+      <c r="AF5" t="s">
         <v>245</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AG5" t="s">
         <v>246</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>247</v>
       </c>
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
@@ -8540,7 +8537,7 @@
         <v>120</v>
       </c>
       <c r="AL5" s="30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AM5" s="30">
         <v>112.4</v>
@@ -8559,7 +8556,7 @@
       </c>
       <c r="AR5" s="17"/>
       <c r="AS5" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AT5" s="35">
         <v>0.40277777777777779</v>
@@ -8578,15 +8575,15 @@
       </c>
       <c r="AY5" s="17"/>
       <c r="AZ5" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="BA5" s="40" t="s">
         <v>320</v>
-      </c>
-      <c r="BA5" s="40" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -8604,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -8616,7 +8613,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -8625,7 +8622,7 @@
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -8676,13 +8673,13 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF6" t="s">
         <v>252</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AG6" t="s">
         <v>253</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>254</v>
       </c>
       <c r="AH6" s="13"/>
       <c r="AI6" s="13"/>
@@ -8691,7 +8688,7 @@
         <v>111</v>
       </c>
       <c r="AL6" s="33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AM6" s="33">
         <v>113.1</v>
@@ -8710,7 +8707,7 @@
       </c>
       <c r="AR6" s="17"/>
       <c r="AS6" s="32" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AT6" s="36">
         <v>0.30208333333333331</v>
@@ -8729,15 +8726,15 @@
       </c>
       <c r="AY6" s="17"/>
       <c r="AZ6" s="40" t="s">
+        <v>321</v>
+      </c>
+      <c r="BA6" s="40" t="s">
         <v>322</v>
-      </c>
-      <c r="BA6" s="40" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -8755,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H7">
         <v>12</v>
@@ -8767,7 +8764,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -8794,7 +8791,7 @@
         <v>3</v>
       </c>
       <c r="T7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U7">
         <v>1</v>
@@ -8827,13 +8824,13 @@
         <v>-1</v>
       </c>
       <c r="AE7" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF7" t="s">
         <v>258</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AG7" t="s">
         <v>259</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>260</v>
       </c>
       <c r="AH7" s="13"/>
       <c r="AI7" s="13"/>
@@ -8842,7 +8839,7 @@
         <v>69</v>
       </c>
       <c r="AL7" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AM7" s="30">
         <v>114</v>
@@ -8861,7 +8858,7 @@
       </c>
       <c r="AR7" s="17"/>
       <c r="AS7" s="29" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AT7" s="35">
         <v>0.2638888888888889</v>
@@ -8880,15 +8877,15 @@
       </c>
       <c r="AY7" s="17"/>
       <c r="AZ7" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BA7" s="40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:53" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
         <v>152</v>
@@ -8906,7 +8903,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -8984,7 +8981,7 @@
         <v>156</v>
       </c>
       <c r="AG8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH8" s="13"/>
       <c r="AI8" s="13"/>
@@ -8993,7 +8990,7 @@
         <v>159</v>
       </c>
       <c r="AL8" s="33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AM8" s="33">
         <v>106.1</v>
@@ -9012,7 +9009,7 @@
       </c>
       <c r="AR8" s="17"/>
       <c r="AS8" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AT8" s="11"/>
       <c r="AU8" s="25"/>
@@ -9025,7 +9022,7 @@
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" t="s">
         <v>141</v>
@@ -9043,7 +9040,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -9118,10 +9115,10 @@
         <v>116</v>
       </c>
       <c r="AF9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AH9" s="13"/>
       <c r="AI9" s="13"/>
@@ -9130,7 +9127,7 @@
         <v>151</v>
       </c>
       <c r="AL9" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AM9" s="30">
         <v>102.7</v>
@@ -9149,10 +9146,10 @@
       </c>
       <c r="AR9" s="17"/>
       <c r="AS9" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AT9" s="33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AU9" s="33">
         <v>18</v>
@@ -9172,7 +9169,7 @@
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B10" t="s">
         <v>85</v>
@@ -9190,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H10">
         <v>14</v>
@@ -9202,7 +9199,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -9262,13 +9259,13 @@
         <v>1</v>
       </c>
       <c r="AE10" t="s">
+        <v>269</v>
+      </c>
+      <c r="AF10" t="s">
         <v>270</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AG10" t="s">
         <v>271</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>272</v>
       </c>
       <c r="AH10" s="13"/>
       <c r="AI10" s="13"/>
@@ -9277,7 +9274,7 @@
         <v>97</v>
       </c>
       <c r="AL10" s="33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AM10" s="33">
         <v>98.5</v>
@@ -9296,10 +9293,10 @@
       </c>
       <c r="AR10" s="17"/>
       <c r="AS10" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AT10" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AU10" s="30">
         <v>11</v>
@@ -9319,7 +9316,7 @@
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
         <v>160</v>
@@ -9337,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -9415,7 +9412,7 @@
         <v>156</v>
       </c>
       <c r="AG11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH11" s="13"/>
       <c r="AI11" s="13"/>
@@ -9424,7 +9421,7 @@
         <v>140</v>
       </c>
       <c r="AL11" s="30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM11" s="30">
         <v>97.6</v>
@@ -9443,10 +9440,10 @@
       </c>
       <c r="AR11" s="17"/>
       <c r="AS11" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AT11" s="33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AU11" s="33">
         <v>-2</v>
@@ -9466,7 +9463,7 @@
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B12" t="s">
         <v>167</v>
@@ -9484,7 +9481,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -9562,7 +9559,7 @@
         <v>156</v>
       </c>
       <c r="AG12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH12" s="13"/>
       <c r="AI12" s="13"/>
@@ -9571,7 +9568,7 @@
         <v>83</v>
       </c>
       <c r="AL12" s="33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AM12" s="33">
         <v>96.7</v>
@@ -9601,7 +9598,7 @@
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s">
         <v>121</v>
@@ -9619,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H13">
         <v>4</v>
@@ -9691,13 +9688,13 @@
         <v>4</v>
       </c>
       <c r="AE13" t="s">
+        <v>279</v>
+      </c>
+      <c r="AF13" t="s">
         <v>280</v>
       </c>
-      <c r="AF13" t="s">
-        <v>281</v>
-      </c>
       <c r="AG13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH13" s="13"/>
       <c r="AI13" s="13"/>
@@ -9706,7 +9703,7 @@
         <v>130</v>
       </c>
       <c r="AL13" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AM13" s="30">
         <v>75.3</v>
@@ -9736,7 +9733,7 @@
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B14" t="s">
         <v>99</v>
@@ -9754,7 +9751,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -9829,10 +9826,10 @@
         <v>116</v>
       </c>
       <c r="AF14" t="s">
+        <v>283</v>
+      </c>
+      <c r="AG14" t="s">
         <v>284</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>285</v>
       </c>
       <c r="AH14" s="13"/>
       <c r="AI14" s="13"/>
@@ -9857,7 +9854,7 @@
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B15" t="s">
         <v>176</v>
@@ -9953,7 +9950,7 @@
         <v>156</v>
       </c>
       <c r="AG15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH15" s="13"/>
       <c r="AI15" s="13"/>
@@ -9978,7 +9975,7 @@
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" t="s">
         <v>164</v>
@@ -9996,7 +9993,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -10074,7 +10071,7 @@
         <v>156</v>
       </c>
       <c r="AG16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH16" s="13"/>
       <c r="AI16" s="13"/>
@@ -10099,7 +10096,7 @@
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s">
         <v>171</v>
@@ -10195,7 +10192,7 @@
         <v>174</v>
       </c>
       <c r="AG17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AH17" s="13"/>
       <c r="AI17" s="13"/>
@@ -10220,7 +10217,7 @@
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
         <v>112</v>
@@ -10238,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -10313,10 +10310,10 @@
         <v>93</v>
       </c>
       <c r="AF18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AH18" s="13"/>
       <c r="AI18" s="13"/>
